--- a/EmployeeBillableData_4.xlsx
+++ b/EmployeeBillableData_4.xlsx
@@ -419,10 +419,10 @@
     <t>tejas.dambale@apmosysuat1.com</t>
   </si>
   <si>
-    <t>-TNM-8765432-drytfugih,DEV-MON-ertyu-fsdvs</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Aniruddha, Aniruddha11</t>
+    <t>-TNM-8765432-drytfugih,DEV-TNM-akp2-Testing</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Aniruddha11</t>
   </si>
   <si>
     <t>A-240276</t>
